--- a/artfynd/A 6073-2026 artfynd.xlsx
+++ b/artfynd/A 6073-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3730324</v>
+        <v>68962617</v>
       </c>
       <c r="B2" t="n">
-        <v>103164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221137</v>
+        <v>100137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pallas, 1771</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grinduga SSO-ut, Fjärilsvägen, 400 m NV bron över Kubbobäcken, Gstr</t>
+          <t>SV Åmotsbäcken, Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626844.4497450867</v>
+        <v>626830</v>
       </c>
       <c r="R2" t="n">
-        <v>6721666.983323205</v>
+        <v>6721684</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-06-03</t>
+          <t>2018-01-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-06-03</t>
+          <t>2018-01-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca 300 ex på vägrenen.</t>
+          <t>Satt i en tall bredvid vägen och spanade. Underbar obs på nära håll!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,21 +782,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren, skogsbilväg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Johan Södercrantz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Johan Södercrantz, Sara Svedberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -814,12 +801,7 @@
         <v>15213695</v>
       </c>
       <c r="B3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>47010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626742.2888892959</v>
+        <v>626742</v>
       </c>
       <c r="R3" t="n">
-        <v>6721828.489317828</v>
+        <v>6721828</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,19 +880,9 @@
           <t>2012-06-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-06-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -942,42 +914,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14948563</v>
+        <v>14948562</v>
       </c>
       <c r="B4" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102021</v>
+        <v>102018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1001,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626749.2399613952</v>
+        <v>626749</v>
       </c>
       <c r="R4" t="n">
-        <v>6721826.768714957</v>
+        <v>6721827</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1034,19 +1001,9 @@
           <t>2011-06-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-06-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1078,19 +1035,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>14948562</v>
+        <v>88558200</v>
       </c>
       <c r="B5" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1111,39 +1063,23 @@
           <t>(Scheven, 1777)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fjärilsvägen, Grinduga, Gstr</t>
+          <t>Grinduga fjärilsstigen, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626749.2399613952</v>
+        <v>626770</v>
       </c>
       <c r="R5" t="n">
-        <v>6721826.768714957</v>
+        <v>6721814</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1167,27 +1103,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-06-17</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-06-17</t>
+          <t>2020-07-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vid vägrenen efter fjärilsvägen</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1202,68 +1133,79 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Vesslén</t>
+          <t>Sara Carlson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Göran Vesslén</t>
+          <t>Sara Carlson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88558200</v>
+        <v>14948563</v>
       </c>
       <c r="B6" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102018</v>
+        <v>102021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grinduga fjärilsstigen, Gstr</t>
+          <t>Fjärilsvägen, Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626770.3699342683</v>
+        <v>626749</v>
       </c>
       <c r="R6" t="n">
-        <v>6721813.754664625</v>
+        <v>6721827</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1287,22 +1229,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2011-06-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2011-06-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Vid vägrenen efter fjärilsvägen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,60 +1254,79 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sara Carlson</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Carlson</t>
+          <t>Via Göran Vesslén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91458672</v>
+        <v>14948560</v>
       </c>
       <c r="B7" t="n">
-        <v>105620</v>
+        <v>43285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221137</v>
+        <v>201143</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Ängsblåvinge</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Cyaniris semiargus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hobäckstjärnen, Gstr</t>
+          <t>Fjärilsvägen, Grinduga, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626843</v>
+        <v>626749</v>
       </c>
       <c r="R7" t="n">
-        <v>6721668</v>
+        <v>6721827</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1394,17 +1350,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2003-06-02</t>
+          <t>2011-06-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2003-06-02</t>
+          <t>2011-06-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ny lokal</t>
+          <t>Vid vägrenen efter fjärilsvägen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,57 +1371,43 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kulturmark, vägdike till skogsväg, delvis fuktig delvis torrslänt, i kalkrikt område</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 260053H</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
+          <t>Göran Vesslén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Ståhl</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Via Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97414929</v>
+        <v>3730324</v>
       </c>
       <c r="B8" t="n">
-        <v>105634</v>
+        <v>106140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221141</v>
+        <v>221137</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1473,10 +1415,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hobäckstjärnen 1 km OSO, kontroll majvivelokal nr 8, Gstr</t>
+          <t>Grinduga SSO-ut, Fjärilsvägen, 400 m NV bron över Kubbobäcken, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1486,7 +1442,7 @@
         <v>6721667</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1510,12 +1466,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2011-06-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-06-04</t>
+          <t>2011-06-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 300 ex på vägrenen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,26 +1490,602 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kulturmark, vägdike</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 291887H</t>
+          <t>Vägren, skogsbilväg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3736216</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fjärilsvägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626843</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6721663</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-06-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-06-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor på västra sidan direkt intill vägrenen.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Patrullstig i kraftledning</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Göran Vesslén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91458672</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hobäckstjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626843</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6721668</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2003-06-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2003-06-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ny lokal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägdike till skogsväg, delvis fuktig delvis torrslänt, i kalkrikt område</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 260053H</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>93800416</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hobäckstjärnen OSO, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626846</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6721650</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2005-05-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2005-05-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kulturmark, skogsväg, stort dike med vatten i botten och dess slänt som är torrare</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 280419H</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström, Göran Odelvik</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94019254</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hobäckstjärnen 1 km OSO, kontroll majvlokal 8, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626850</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6721656</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lokalens läge: strax norr om dike som korsar vägen,O-sidan av dike och vägkant. De allra flesta majvivor blommar, i skuggan ärde i knopp, ej hög gräsväxt. Följeartsträden småplantor</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kulturmark, skogsvägkant och slänt mot blött dike</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 286344H</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström, Göran Odelvik</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97414929</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hobäckstjärnen 1 km OSO, kontroll majvivelokal nr 8, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626844</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6721667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2006-06-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägdike</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 291887H</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Magnus Bergström</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Åke Lundblad</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY13" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>

--- a/artfynd/A 6073-2026 artfynd.xlsx
+++ b/artfynd/A 6073-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68962617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15213695</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88558200</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1263,6 +1288,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948563</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1384,6 +1414,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948560</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1505,6 +1540,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3730324</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1636,6 +1676,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3736216</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1752,6 +1797,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91458672</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1863,6 +1913,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93800416</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1979,6 +2034,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94019254</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2090,8 +2150,27 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97414929</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>